--- a/examples/results/Four-stream-Yee-and-Grossmann-1990-1/Solution Metrics.xlsx
+++ b/examples/results/Four-stream-Yee-and-Grossmann-1990-1/Solution Metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3575,6 +3575,3106 @@
         <v>1</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>9.647861003875732</v>
+      </c>
+      <c r="E102" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>7.448047876358032</v>
+      </c>
+      <c r="E103" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>11.33115935325623</v>
+      </c>
+      <c r="E104" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F104" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D105" t="n">
+        <v>11.6989917755127</v>
+      </c>
+      <c r="E105" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9.24504828453064</v>
+      </c>
+      <c r="E106" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D107" t="n">
+        <v>11.32202410697937</v>
+      </c>
+      <c r="E107" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>11.01660108566284</v>
+      </c>
+      <c r="E108" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>11.61975002288818</v>
+      </c>
+      <c r="E109" t="n">
+        <v>163556.1244467395</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>11.09060001373291</v>
+      </c>
+      <c r="E110" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D111" t="n">
+        <v>8.736273527145386</v>
+      </c>
+      <c r="E111" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>6</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4.74050760269165</v>
+      </c>
+      <c r="E112" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>6</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4.180033445358276</v>
+      </c>
+      <c r="E113" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>6</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D114" t="n">
+        <v>9.88239049911499</v>
+      </c>
+      <c r="E114" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>6</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>7.885836362838745</v>
+      </c>
+      <c r="E115" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F115" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>6</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>10.08879375457764</v>
+      </c>
+      <c r="E116" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>6</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>7.178004264831543</v>
+      </c>
+      <c r="E117" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F117" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" t="n">
+        <v>4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>6</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>8.062750101089478</v>
+      </c>
+      <c r="E118" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>6</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>6.470174312591553</v>
+      </c>
+      <c r="E119" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>6</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D120" t="n">
+        <v>9.191350221633911</v>
+      </c>
+      <c r="E120" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>6</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8.185158252716064</v>
+      </c>
+      <c r="E121" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>4</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>6.042858600616455</v>
+      </c>
+      <c r="E122" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F122" t="n">
+        <v>3</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>4</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5.580738067626953</v>
+      </c>
+      <c r="E123" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>4</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8.160580396652222</v>
+      </c>
+      <c r="E124" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5.983443975448608</v>
+      </c>
+      <c r="E125" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3</v>
+      </c>
+      <c r="G125" t="n">
+        <v>5</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>6.972531318664551</v>
+      </c>
+      <c r="E126" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>10</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.778868436813354</v>
+      </c>
+      <c r="E127" t="n">
+        <v>154853.8603588039</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" t="n">
+        <v>3</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D128" t="n">
+        <v>9.521347999572754</v>
+      </c>
+      <c r="E128" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>4</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>9.687875986099243</v>
+      </c>
+      <c r="E129" t="n">
+        <v>163556.1230604507</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D130" t="n">
+        <v>9.285595178604126</v>
+      </c>
+      <c r="E130" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>10.39598250389099</v>
+      </c>
+      <c r="E131" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>10</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.963991641998291</v>
+      </c>
+      <c r="E132" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>10</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.905758380889893</v>
+      </c>
+      <c r="E133" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D134" t="n">
+        <v>10.58432579040527</v>
+      </c>
+      <c r="E134" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>10</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.871210813522339</v>
+      </c>
+      <c r="E135" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>10</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2.385619878768921</v>
+      </c>
+      <c r="E136" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>10</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2.906245470046997</v>
+      </c>
+      <c r="E137" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>10</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.37697172164917</v>
+      </c>
+      <c r="E138" t="n">
+        <v>154853.8594101579</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" t="n">
+        <v>3</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>10</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.058948516845703</v>
+      </c>
+      <c r="E139" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>10</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2.768038034439087</v>
+      </c>
+      <c r="E140" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3.866219758987427</v>
+      </c>
+      <c r="E141" t="n">
+        <v>160353.3356834063</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3</v>
+      </c>
+      <c r="G141" t="n">
+        <v>4</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>8</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D142" t="n">
+        <v>6.105318307876587</v>
+      </c>
+      <c r="E142" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>2</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>8</v>
+      </c>
+      <c r="C143" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>5.90412712097168</v>
+      </c>
+      <c r="E143" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>8</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D144" t="n">
+        <v>6.373793363571167</v>
+      </c>
+      <c r="E144" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>8</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D145" t="n">
+        <v>9.677002668380737</v>
+      </c>
+      <c r="E145" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3</v>
+      </c>
+      <c r="G145" t="n">
+        <v>4</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>8</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D146" t="n">
+        <v>8.410236597061157</v>
+      </c>
+      <c r="E146" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3</v>
+      </c>
+      <c r="G146" t="n">
+        <v>4</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>8</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8.280142307281494</v>
+      </c>
+      <c r="E147" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3</v>
+      </c>
+      <c r="G147" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>8</v>
+      </c>
+      <c r="C148" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D148" t="n">
+        <v>7.471914052963257</v>
+      </c>
+      <c r="E148" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>8</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D149" t="n">
+        <v>9.605321407318115</v>
+      </c>
+      <c r="E149" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>8</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>10.00810718536377</v>
+      </c>
+      <c r="E150" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3</v>
+      </c>
+      <c r="G150" t="n">
+        <v>5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>2</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>8</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D151" t="n">
+        <v>11.61031126976013</v>
+      </c>
+      <c r="E151" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F151" t="n">
+        <v>3</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" t="n">
+        <v>2</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>14</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D152" t="n">
+        <v>6.216550827026367</v>
+      </c>
+      <c r="E152" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F152" t="n">
+        <v>3</v>
+      </c>
+      <c r="G152" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>14</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>5.555490493774414</v>
+      </c>
+      <c r="E153" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" t="n">
+        <v>3</v>
+      </c>
+      <c r="H153" t="n">
+        <v>2</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>14</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D154" t="n">
+        <v>9.482042789459229</v>
+      </c>
+      <c r="E154" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F154" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" t="n">
+        <v>5</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>14</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>6.484854936599731</v>
+      </c>
+      <c r="E155" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F155" t="n">
+        <v>3</v>
+      </c>
+      <c r="G155" t="n">
+        <v>3</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>12</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2.033271789550781</v>
+      </c>
+      <c r="E156" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F156" t="n">
+        <v>3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>14</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D157" t="n">
+        <v>8.977032423019409</v>
+      </c>
+      <c r="E157" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F157" t="n">
+        <v>3</v>
+      </c>
+      <c r="G157" t="n">
+        <v>4</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>14</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>8.482153415679932</v>
+      </c>
+      <c r="E158" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F158" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" t="n">
+        <v>5</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>14</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>6.556637525558472</v>
+      </c>
+      <c r="E159" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F159" t="n">
+        <v>3</v>
+      </c>
+      <c r="G159" t="n">
+        <v>5</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>14</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D160" t="n">
+        <v>10.0616557598114</v>
+      </c>
+      <c r="E160" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F160" t="n">
+        <v>3</v>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>14</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>8.845618486404419</v>
+      </c>
+      <c r="E161" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F161" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5</v>
+      </c>
+      <c r="H161" t="n">
+        <v>2</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>14</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D162" t="n">
+        <v>10.64946484565735</v>
+      </c>
+      <c r="E162" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F162" t="n">
+        <v>3</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>12</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>3.838194370269775</v>
+      </c>
+      <c r="E163" t="n">
+        <v>154853.8603588039</v>
+      </c>
+      <c r="F163" t="n">
+        <v>3</v>
+      </c>
+      <c r="G163" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" t="n">
+        <v>2</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>12</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.442211627960205</v>
+      </c>
+      <c r="E164" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F164" t="n">
+        <v>3</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>12</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D165" t="n">
+        <v>3.046076536178589</v>
+      </c>
+      <c r="E165" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F165" t="n">
+        <v>3</v>
+      </c>
+      <c r="G165" t="n">
+        <v>3</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>12</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D166" t="n">
+        <v>3.034258842468262</v>
+      </c>
+      <c r="E166" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F166" t="n">
+        <v>3</v>
+      </c>
+      <c r="G166" t="n">
+        <v>3</v>
+      </c>
+      <c r="H166" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>12</v>
+      </c>
+      <c r="C167" t="n">
+        <v>4</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.635405778884888</v>
+      </c>
+      <c r="E167" t="n">
+        <v>160353.3355381816</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3</v>
+      </c>
+      <c r="G167" t="n">
+        <v>4</v>
+      </c>
+      <c r="H167" t="n">
+        <v>2</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>12</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3.426810026168823</v>
+      </c>
+      <c r="E168" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F168" t="n">
+        <v>3</v>
+      </c>
+      <c r="G168" t="n">
+        <v>3</v>
+      </c>
+      <c r="H168" t="n">
+        <v>2</v>
+      </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>12</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3.843072891235352</v>
+      </c>
+      <c r="E169" t="n">
+        <v>154853.8595986348</v>
+      </c>
+      <c r="F169" t="n">
+        <v>3</v>
+      </c>
+      <c r="G169" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" t="n">
+        <v>2</v>
+      </c>
+      <c r="I169" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>12</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3.037919044494629</v>
+      </c>
+      <c r="E170" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F170" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3</v>
+      </c>
+      <c r="H170" t="n">
+        <v>2</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>12</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.735475301742554</v>
+      </c>
+      <c r="E171" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F171" t="n">
+        <v>3</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>18</v>
+      </c>
+      <c r="C172" t="n">
+        <v>4</v>
+      </c>
+      <c r="D172" t="n">
+        <v>5.632369041442871</v>
+      </c>
+      <c r="E172" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F172" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>18</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>6.89192008972168</v>
+      </c>
+      <c r="E173" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F173" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>18</v>
+      </c>
+      <c r="C174" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D174" t="n">
+        <v>7.334528923034668</v>
+      </c>
+      <c r="E174" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F174" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" t="n">
+        <v>3</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>18</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D175" t="n">
+        <v>7.033608675003052</v>
+      </c>
+      <c r="E175" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F175" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" t="n">
+        <v>3</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>18</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>9.627535820007324</v>
+      </c>
+      <c r="E176" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F176" t="n">
+        <v>3</v>
+      </c>
+      <c r="G176" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>18</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D177" t="n">
+        <v>7.99564266204834</v>
+      </c>
+      <c r="E177" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F177" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" t="n">
+        <v>4</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>18</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D178" t="n">
+        <v>8.870957136154175</v>
+      </c>
+      <c r="E178" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2</v>
+      </c>
+      <c r="I178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>18</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>9.019889116287231</v>
+      </c>
+      <c r="E179" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F179" t="n">
+        <v>3</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
+        <v>2</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>18</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>9.444482803344727</v>
+      </c>
+      <c r="E180" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F180" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" t="n">
+        <v>3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>18</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D181" t="n">
+        <v>9.697831153869629</v>
+      </c>
+      <c r="E181" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F181" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D182" t="n">
+        <v>4.785123109817505</v>
+      </c>
+      <c r="E182" t="n">
+        <v>154853.8518716671</v>
+      </c>
+      <c r="F182" t="n">
+        <v>3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D183" t="n">
+        <v>4.090834617614746</v>
+      </c>
+      <c r="E183" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F183" t="n">
+        <v>3</v>
+      </c>
+      <c r="G183" t="n">
+        <v>3</v>
+      </c>
+      <c r="H183" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4.004571914672852</v>
+      </c>
+      <c r="E184" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F184" t="n">
+        <v>3</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3</v>
+      </c>
+      <c r="H184" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D185" t="n">
+        <v>4.705978631973267</v>
+      </c>
+      <c r="E185" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F185" t="n">
+        <v>3</v>
+      </c>
+      <c r="G185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.979263305664062</v>
+      </c>
+      <c r="E186" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3</v>
+      </c>
+      <c r="G186" t="n">
+        <v>3</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D187" t="n">
+        <v>4.814168214797974</v>
+      </c>
+      <c r="E187" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F187" t="n">
+        <v>3</v>
+      </c>
+      <c r="G187" t="n">
+        <v>4</v>
+      </c>
+      <c r="H187" t="n">
+        <v>2</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D188" t="n">
+        <v>4.440430641174316</v>
+      </c>
+      <c r="E188" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F188" t="n">
+        <v>3</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5.154278755187988</v>
+      </c>
+      <c r="E189" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F189" t="n">
+        <v>3</v>
+      </c>
+      <c r="G189" t="n">
+        <v>3</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" t="n">
+        <v>3.523710012435913</v>
+      </c>
+      <c r="E190" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F190" t="n">
+        <v>3</v>
+      </c>
+      <c r="G190" t="n">
+        <v>3</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>7.049277782440186</v>
+      </c>
+      <c r="E191" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F191" t="n">
+        <v>3</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" t="n">
+        <v>2</v>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>20</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D192" t="n">
+        <v>5.057834625244141</v>
+      </c>
+      <c r="E192" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F192" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4</v>
+      </c>
+      <c r="H192" t="n">
+        <v>2</v>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>20</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D193" t="n">
+        <v>6.275627851486206</v>
+      </c>
+      <c r="E193" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F193" t="n">
+        <v>3</v>
+      </c>
+      <c r="G193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2</v>
+      </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>20</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>6.426144361495972</v>
+      </c>
+      <c r="E194" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F194" t="n">
+        <v>3</v>
+      </c>
+      <c r="G194" t="n">
+        <v>3</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>20</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D195" t="n">
+        <v>8.565037727355957</v>
+      </c>
+      <c r="E195" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F195" t="n">
+        <v>3</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>20</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D196" t="n">
+        <v>8.389993906021118</v>
+      </c>
+      <c r="E196" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3</v>
+      </c>
+      <c r="G196" t="n">
+        <v>3</v>
+      </c>
+      <c r="H196" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>20</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>8.632272481918335</v>
+      </c>
+      <c r="E197" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F197" t="n">
+        <v>3</v>
+      </c>
+      <c r="G197" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" t="n">
+        <v>2</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>20</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D198" t="n">
+        <v>9.594111442565918</v>
+      </c>
+      <c r="E198" t="n">
+        <v>163556.1244363221</v>
+      </c>
+      <c r="F198" t="n">
+        <v>3</v>
+      </c>
+      <c r="G198" t="n">
+        <v>5</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>20</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4</v>
+      </c>
+      <c r="D199" t="n">
+        <v>6.061440467834473</v>
+      </c>
+      <c r="E199" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F199" t="n">
+        <v>3</v>
+      </c>
+      <c r="G199" t="n">
+        <v>3</v>
+      </c>
+      <c r="H199" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>20</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D200" t="n">
+        <v>9.678464889526367</v>
+      </c>
+      <c r="E200" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>25/08/2025 15:41:31</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>20</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>9.688214302062988</v>
+      </c>
+      <c r="E201" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" t="n">
+        <v>5</v>
+      </c>
+      <c r="H201" t="n">
+        <v>2</v>
+      </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/results/Four-stream-Yee-and-Grossmann-1990-1/Solution Metrics.xlsx
+++ b/examples/results/Four-stream-Yee-and-Grossmann-1990-1/Solution Metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6675,6 +6675,3106 @@
         <v>1</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D202" t="n">
+        <v>6.170011281967163</v>
+      </c>
+      <c r="E202" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F202" t="n">
+        <v>3</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2</v>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D203" t="n">
+        <v>7.718672752380371</v>
+      </c>
+      <c r="E203" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+      <c r="G203" t="n">
+        <v>4</v>
+      </c>
+      <c r="H203" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5.651273965835571</v>
+      </c>
+      <c r="E204" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F204" t="n">
+        <v>3</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3</v>
+      </c>
+      <c r="H204" t="n">
+        <v>2</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>2</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D205" t="n">
+        <v>7.661832094192505</v>
+      </c>
+      <c r="E205" t="n">
+        <v>163556.1244467395</v>
+      </c>
+      <c r="F205" t="n">
+        <v>3</v>
+      </c>
+      <c r="G205" t="n">
+        <v>5</v>
+      </c>
+      <c r="H205" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D206" t="n">
+        <v>7.939606189727783</v>
+      </c>
+      <c r="E206" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F206" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" t="n">
+        <v>3</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>7.464914798736572</v>
+      </c>
+      <c r="E207" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F207" t="n">
+        <v>3</v>
+      </c>
+      <c r="G207" t="n">
+        <v>5</v>
+      </c>
+      <c r="H207" t="n">
+        <v>2</v>
+      </c>
+      <c r="I207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2</v>
+      </c>
+      <c r="C208" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D208" t="n">
+        <v>8.456570386886597</v>
+      </c>
+      <c r="E208" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F208" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>3</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2</v>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>4.42988109588623</v>
+      </c>
+      <c r="E209" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F209" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" t="n">
+        <v>5</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5.735851049423218</v>
+      </c>
+      <c r="E210" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G210" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>2</v>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2</v>
+      </c>
+      <c r="C211" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>7.048279762268066</v>
+      </c>
+      <c r="E211" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F211" t="n">
+        <v>3</v>
+      </c>
+      <c r="G211" t="n">
+        <v>5</v>
+      </c>
+      <c r="H211" t="n">
+        <v>2</v>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>4</v>
+      </c>
+      <c r="C212" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D212" t="n">
+        <v>5.317568063735962</v>
+      </c>
+      <c r="E212" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F212" t="n">
+        <v>3</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
+        <v>2</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>5.382221698760986</v>
+      </c>
+      <c r="E213" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F213" t="n">
+        <v>3</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3</v>
+      </c>
+      <c r="H213" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>4</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4</v>
+      </c>
+      <c r="D214" t="n">
+        <v>4.813600301742554</v>
+      </c>
+      <c r="E214" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F214" t="n">
+        <v>3</v>
+      </c>
+      <c r="G214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>2</v>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>7.500988245010376</v>
+      </c>
+      <c r="E215" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F215" t="n">
+        <v>3</v>
+      </c>
+      <c r="G215" t="n">
+        <v>3</v>
+      </c>
+      <c r="H215" t="n">
+        <v>2</v>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>4</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D216" t="n">
+        <v>8.642781734466553</v>
+      </c>
+      <c r="E216" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F216" t="n">
+        <v>3</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>4</v>
+      </c>
+      <c r="C217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D217" t="n">
+        <v>9.552728652954102</v>
+      </c>
+      <c r="E217" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F217" t="n">
+        <v>3</v>
+      </c>
+      <c r="G217" t="n">
+        <v>3</v>
+      </c>
+      <c r="H217" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>4</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D218" t="n">
+        <v>6.601475477218628</v>
+      </c>
+      <c r="E218" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3</v>
+      </c>
+      <c r="G218" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2</v>
+      </c>
+      <c r="I218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>4</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D219" t="n">
+        <v>8.429941892623901</v>
+      </c>
+      <c r="E219" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F219" t="n">
+        <v>3</v>
+      </c>
+      <c r="G219" t="n">
+        <v>5</v>
+      </c>
+      <c r="H219" t="n">
+        <v>2</v>
+      </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>4</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D220" t="n">
+        <v>9.839011192321777</v>
+      </c>
+      <c r="E220" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F220" t="n">
+        <v>3</v>
+      </c>
+      <c r="G220" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>4</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D221" t="n">
+        <v>9.264752388000488</v>
+      </c>
+      <c r="E221" t="n">
+        <v>163556.1230604507</v>
+      </c>
+      <c r="F221" t="n">
+        <v>3</v>
+      </c>
+      <c r="G221" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>6</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4.245253324508667</v>
+      </c>
+      <c r="E222" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F222" t="n">
+        <v>3</v>
+      </c>
+      <c r="G222" t="n">
+        <v>4</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>6</v>
+      </c>
+      <c r="C223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D223" t="n">
+        <v>6.255726099014282</v>
+      </c>
+      <c r="E223" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F223" t="n">
+        <v>3</v>
+      </c>
+      <c r="G223" t="n">
+        <v>4</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>6</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4</v>
+      </c>
+      <c r="D224" t="n">
+        <v>4.013552904129028</v>
+      </c>
+      <c r="E224" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F224" t="n">
+        <v>3</v>
+      </c>
+      <c r="G224" t="n">
+        <v>3</v>
+      </c>
+      <c r="H224" t="n">
+        <v>2</v>
+      </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>6</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D225" t="n">
+        <v>8.110213994979858</v>
+      </c>
+      <c r="E225" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F225" t="n">
+        <v>3</v>
+      </c>
+      <c r="G225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>6</v>
+      </c>
+      <c r="C226" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D226" t="n">
+        <v>6.047060012817383</v>
+      </c>
+      <c r="E226" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F226" t="n">
+        <v>3</v>
+      </c>
+      <c r="G226" t="n">
+        <v>4</v>
+      </c>
+      <c r="H226" t="n">
+        <v>2</v>
+      </c>
+      <c r="I226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D227" t="n">
+        <v>7.141663312911987</v>
+      </c>
+      <c r="E227" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F227" t="n">
+        <v>3</v>
+      </c>
+      <c r="G227" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" t="n">
+        <v>2</v>
+      </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>6</v>
+      </c>
+      <c r="C228" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>7.352396249771118</v>
+      </c>
+      <c r="E228" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F228" t="n">
+        <v>3</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>6</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D229" t="n">
+        <v>8.553641080856323</v>
+      </c>
+      <c r="E229" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F229" t="n">
+        <v>3</v>
+      </c>
+      <c r="G229" t="n">
+        <v>4</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2</v>
+      </c>
+      <c r="I229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>6</v>
+      </c>
+      <c r="C230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D230" t="n">
+        <v>7.534297466278076</v>
+      </c>
+      <c r="E230" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F230" t="n">
+        <v>3</v>
+      </c>
+      <c r="G230" t="n">
+        <v>4</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>6</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D231" t="n">
+        <v>8.643829345703125</v>
+      </c>
+      <c r="E231" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F231" t="n">
+        <v>3</v>
+      </c>
+      <c r="G231" t="n">
+        <v>5</v>
+      </c>
+      <c r="H231" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>14</v>
+      </c>
+      <c r="C232" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D232" t="n">
+        <v>5.603986263275146</v>
+      </c>
+      <c r="E232" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F232" t="n">
+        <v>3</v>
+      </c>
+      <c r="G232" t="n">
+        <v>3</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>14</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D233" t="n">
+        <v>5.529096841812134</v>
+      </c>
+      <c r="E233" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3</v>
+      </c>
+      <c r="H233" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>14</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D234" t="n">
+        <v>5.440103769302368</v>
+      </c>
+      <c r="E234" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G234" t="n">
+        <v>3</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>14</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D235" t="n">
+        <v>9.208802461624146</v>
+      </c>
+      <c r="E235" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F235" t="n">
+        <v>3</v>
+      </c>
+      <c r="G235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>14</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" t="n">
+        <v>5.651120185852051</v>
+      </c>
+      <c r="E236" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F236" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" t="n">
+        <v>5</v>
+      </c>
+      <c r="H236" t="n">
+        <v>2</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>14</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>7.444757461547852</v>
+      </c>
+      <c r="E237" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3</v>
+      </c>
+      <c r="G237" t="n">
+        <v>5</v>
+      </c>
+      <c r="H237" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>14</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D238" t="n">
+        <v>7.860393285751343</v>
+      </c>
+      <c r="E238" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F238" t="n">
+        <v>3</v>
+      </c>
+      <c r="G238" t="n">
+        <v>5</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>14</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D239" t="n">
+        <v>7.604028224945068</v>
+      </c>
+      <c r="E239" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F239" t="n">
+        <v>3</v>
+      </c>
+      <c r="G239" t="n">
+        <v>5</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2</v>
+      </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>14</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D240" t="n">
+        <v>8.116040706634521</v>
+      </c>
+      <c r="E240" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F240" t="n">
+        <v>3</v>
+      </c>
+      <c r="G240" t="n">
+        <v>5</v>
+      </c>
+      <c r="H240" t="n">
+        <v>2</v>
+      </c>
+      <c r="I240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>14</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D241" t="n">
+        <v>8.137558937072754</v>
+      </c>
+      <c r="E241" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G241" t="n">
+        <v>4</v>
+      </c>
+      <c r="H241" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>10</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2.536484241485596</v>
+      </c>
+      <c r="E242" t="n">
+        <v>154853.8603588039</v>
+      </c>
+      <c r="F242" t="n">
+        <v>3</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" t="n">
+        <v>2</v>
+      </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>10</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D243" t="n">
+        <v>2.870254278182983</v>
+      </c>
+      <c r="E243" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F243" t="n">
+        <v>3</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H243" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>10</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D244" t="n">
+        <v>2.858397960662842</v>
+      </c>
+      <c r="E244" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F244" t="n">
+        <v>3</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>10</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.442142009735107</v>
+      </c>
+      <c r="E245" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F245" t="n">
+        <v>3</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3</v>
+      </c>
+      <c r="H245" t="n">
+        <v>2</v>
+      </c>
+      <c r="I245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>10</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.056020259857178</v>
+      </c>
+      <c r="E246" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F246" t="n">
+        <v>3</v>
+      </c>
+      <c r="G246" t="n">
+        <v>3</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>10</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1.96857762336731</v>
+      </c>
+      <c r="E247" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3</v>
+      </c>
+      <c r="H247" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>10</v>
+      </c>
+      <c r="C248" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2.968591451644897</v>
+      </c>
+      <c r="E248" t="n">
+        <v>154853.8594101579</v>
+      </c>
+      <c r="F248" t="n">
+        <v>3</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>10</v>
+      </c>
+      <c r="C249" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2.792069673538208</v>
+      </c>
+      <c r="E249" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3</v>
+      </c>
+      <c r="G249" t="n">
+        <v>5</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>10</v>
+      </c>
+      <c r="C250" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3.573943853378296</v>
+      </c>
+      <c r="E250" t="n">
+        <v>160353.3356834063</v>
+      </c>
+      <c r="F250" t="n">
+        <v>3</v>
+      </c>
+      <c r="G250" t="n">
+        <v>4</v>
+      </c>
+      <c r="H250" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2.641834020614624</v>
+      </c>
+      <c r="E251" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F251" t="n">
+        <v>3</v>
+      </c>
+      <c r="G251" t="n">
+        <v>3</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>8</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D252" t="n">
+        <v>5.878151416778564</v>
+      </c>
+      <c r="E252" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3</v>
+      </c>
+      <c r="H252" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>8</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D253" t="n">
+        <v>5.750422716140747</v>
+      </c>
+      <c r="E253" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>8</v>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" t="n">
+        <v>5.460059404373169</v>
+      </c>
+      <c r="E254" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>8</v>
+      </c>
+      <c r="C255" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D255" t="n">
+        <v>7.362058877944946</v>
+      </c>
+      <c r="E255" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F255" t="n">
+        <v>3</v>
+      </c>
+      <c r="G255" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>8</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D256" t="n">
+        <v>8.636627912521362</v>
+      </c>
+      <c r="E256" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3</v>
+      </c>
+      <c r="G256" t="n">
+        <v>4</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>8</v>
+      </c>
+      <c r="C257" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D257" t="n">
+        <v>7.342742443084717</v>
+      </c>
+      <c r="E257" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F257" t="n">
+        <v>3</v>
+      </c>
+      <c r="G257" t="n">
+        <v>5</v>
+      </c>
+      <c r="H257" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>8</v>
+      </c>
+      <c r="C258" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D258" t="n">
+        <v>7.053425788879395</v>
+      </c>
+      <c r="E258" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F258" t="n">
+        <v>3</v>
+      </c>
+      <c r="G258" t="n">
+        <v>3</v>
+      </c>
+      <c r="H258" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>8</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D259" t="n">
+        <v>8.390944719314575</v>
+      </c>
+      <c r="E259" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F259" t="n">
+        <v>3</v>
+      </c>
+      <c r="G259" t="n">
+        <v>5</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>12</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1.662823677062988</v>
+      </c>
+      <c r="E260" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F260" t="n">
+        <v>3</v>
+      </c>
+      <c r="G260" t="n">
+        <v>3</v>
+      </c>
+      <c r="H260" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>8</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D261" t="n">
+        <v>9.277550935745239</v>
+      </c>
+      <c r="E261" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F261" t="n">
+        <v>3</v>
+      </c>
+      <c r="G261" t="n">
+        <v>4</v>
+      </c>
+      <c r="H261" t="n">
+        <v>2</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>12</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.37329363822937</v>
+      </c>
+      <c r="E262" t="n">
+        <v>154853.8603588039</v>
+      </c>
+      <c r="F262" t="n">
+        <v>3</v>
+      </c>
+      <c r="G262" t="n">
+        <v>3</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>8</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D263" t="n">
+        <v>8.494283199310303</v>
+      </c>
+      <c r="E263" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F263" t="n">
+        <v>3</v>
+      </c>
+      <c r="G263" t="n">
+        <v>5</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>12</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D264" t="n">
+        <v>2.675899744033813</v>
+      </c>
+      <c r="E264" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3</v>
+      </c>
+      <c r="G264" t="n">
+        <v>3</v>
+      </c>
+      <c r="H264" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>12</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D265" t="n">
+        <v>2.481427907943726</v>
+      </c>
+      <c r="E265" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F265" t="n">
+        <v>3</v>
+      </c>
+      <c r="G265" t="n">
+        <v>4</v>
+      </c>
+      <c r="H265" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>12</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2.975486516952515</v>
+      </c>
+      <c r="E266" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>12</v>
+      </c>
+      <c r="C267" t="n">
+        <v>4</v>
+      </c>
+      <c r="D267" t="n">
+        <v>2.470512628555298</v>
+      </c>
+      <c r="E267" t="n">
+        <v>160353.3355381816</v>
+      </c>
+      <c r="F267" t="n">
+        <v>3</v>
+      </c>
+      <c r="G267" t="n">
+        <v>4</v>
+      </c>
+      <c r="H267" t="n">
+        <v>2</v>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>12</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D268" t="n">
+        <v>3.094410181045532</v>
+      </c>
+      <c r="E268" t="n">
+        <v>154853.8605729445</v>
+      </c>
+      <c r="F268" t="n">
+        <v>3</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>12</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3.311568737030029</v>
+      </c>
+      <c r="E269" t="n">
+        <v>154853.8595986348</v>
+      </c>
+      <c r="F269" t="n">
+        <v>3</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3</v>
+      </c>
+      <c r="H269" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>12</v>
+      </c>
+      <c r="C270" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D270" t="n">
+        <v>3.710716009140015</v>
+      </c>
+      <c r="E270" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3</v>
+      </c>
+      <c r="G270" t="n">
+        <v>4</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2</v>
+      </c>
+      <c r="I270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>12</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2.786479473114014</v>
+      </c>
+      <c r="E271" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F271" t="n">
+        <v>3</v>
+      </c>
+      <c r="G271" t="n">
+        <v>3</v>
+      </c>
+      <c r="H271" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>18</v>
+      </c>
+      <c r="C272" t="n">
+        <v>4</v>
+      </c>
+      <c r="D272" t="n">
+        <v>5.113462924957275</v>
+      </c>
+      <c r="E272" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3</v>
+      </c>
+      <c r="G272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H272" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>18</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6.025393724441528</v>
+      </c>
+      <c r="E273" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F273" t="n">
+        <v>3</v>
+      </c>
+      <c r="G273" t="n">
+        <v>3</v>
+      </c>
+      <c r="H273" t="n">
+        <v>2</v>
+      </c>
+      <c r="I273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>18</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D274" t="n">
+        <v>7.322849273681641</v>
+      </c>
+      <c r="E274" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F274" t="n">
+        <v>3</v>
+      </c>
+      <c r="G274" t="n">
+        <v>5</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>18</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D275" t="n">
+        <v>5.911355495452881</v>
+      </c>
+      <c r="E275" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F275" t="n">
+        <v>3</v>
+      </c>
+      <c r="G275" t="n">
+        <v>3</v>
+      </c>
+      <c r="H275" t="n">
+        <v>2</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>18</v>
+      </c>
+      <c r="C276" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D276" t="n">
+        <v>7.185731172561646</v>
+      </c>
+      <c r="E276" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F276" t="n">
+        <v>3</v>
+      </c>
+      <c r="G276" t="n">
+        <v>4</v>
+      </c>
+      <c r="H276" t="n">
+        <v>2</v>
+      </c>
+      <c r="I276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>18</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>8.412850856781006</v>
+      </c>
+      <c r="E277" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F277" t="n">
+        <v>3</v>
+      </c>
+      <c r="G277" t="n">
+        <v>5</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>18</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D278" t="n">
+        <v>8.005556344985962</v>
+      </c>
+      <c r="E278" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F278" t="n">
+        <v>3</v>
+      </c>
+      <c r="G278" t="n">
+        <v>3</v>
+      </c>
+      <c r="H278" t="n">
+        <v>2</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>18</v>
+      </c>
+      <c r="C279" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D279" t="n">
+        <v>6.504921197891235</v>
+      </c>
+      <c r="E279" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F279" t="n">
+        <v>3</v>
+      </c>
+      <c r="G279" t="n">
+        <v>3</v>
+      </c>
+      <c r="H279" t="n">
+        <v>2</v>
+      </c>
+      <c r="I279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>18</v>
+      </c>
+      <c r="C280" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D280" t="n">
+        <v>8.936293840408325</v>
+      </c>
+      <c r="E280" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F280" t="n">
+        <v>3</v>
+      </c>
+      <c r="G280" t="n">
+        <v>3</v>
+      </c>
+      <c r="H280" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>18</v>
+      </c>
+      <c r="C281" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D281" t="n">
+        <v>8.982512235641479</v>
+      </c>
+      <c r="E281" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F281" t="n">
+        <v>3</v>
+      </c>
+      <c r="G281" t="n">
+        <v>4</v>
+      </c>
+      <c r="H281" t="n">
+        <v>2</v>
+      </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>16</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D282" t="n">
+        <v>4.252307176589966</v>
+      </c>
+      <c r="E282" t="n">
+        <v>154853.8518716671</v>
+      </c>
+      <c r="F282" t="n">
+        <v>3</v>
+      </c>
+      <c r="G282" t="n">
+        <v>3</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>16</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D283" t="n">
+        <v>4.254110336303711</v>
+      </c>
+      <c r="E283" t="n">
+        <v>160353.3363877643</v>
+      </c>
+      <c r="F283" t="n">
+        <v>3</v>
+      </c>
+      <c r="G283" t="n">
+        <v>4</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2</v>
+      </c>
+      <c r="I283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>16</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D284" t="n">
+        <v>4.069965124130249</v>
+      </c>
+      <c r="E284" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F284" t="n">
+        <v>3</v>
+      </c>
+      <c r="G284" t="n">
+        <v>3</v>
+      </c>
+      <c r="H284" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>16</v>
+      </c>
+      <c r="C285" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3.770396947860718</v>
+      </c>
+      <c r="E285" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F285" t="n">
+        <v>3</v>
+      </c>
+      <c r="G285" t="n">
+        <v>3</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>16</v>
+      </c>
+      <c r="C286" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D286" t="n">
+        <v>3.980784177780151</v>
+      </c>
+      <c r="E286" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F286" t="n">
+        <v>3</v>
+      </c>
+      <c r="G286" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" t="n">
+        <v>2</v>
+      </c>
+      <c r="I286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>16</v>
+      </c>
+      <c r="C287" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D287" t="n">
+        <v>4.49744987487793</v>
+      </c>
+      <c r="E287" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F287" t="n">
+        <v>3</v>
+      </c>
+      <c r="G287" t="n">
+        <v>3</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>16</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D288" t="n">
+        <v>3.138552665710449</v>
+      </c>
+      <c r="E288" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F288" t="n">
+        <v>3</v>
+      </c>
+      <c r="G288" t="n">
+        <v>3</v>
+      </c>
+      <c r="H288" t="n">
+        <v>2</v>
+      </c>
+      <c r="I288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>16</v>
+      </c>
+      <c r="C289" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D289" t="n">
+        <v>4.557208299636841</v>
+      </c>
+      <c r="E289" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F289" t="n">
+        <v>3</v>
+      </c>
+      <c r="G289" t="n">
+        <v>3</v>
+      </c>
+      <c r="H289" t="n">
+        <v>2</v>
+      </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>16</v>
+      </c>
+      <c r="C290" t="n">
+        <v>4</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3.152394771575928</v>
+      </c>
+      <c r="E290" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F290" t="n">
+        <v>3</v>
+      </c>
+      <c r="G290" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>16</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D291" t="n">
+        <v>5.998653650283813</v>
+      </c>
+      <c r="E291" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F291" t="n">
+        <v>3</v>
+      </c>
+      <c r="G291" t="n">
+        <v>3</v>
+      </c>
+      <c r="H291" t="n">
+        <v>2</v>
+      </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>20</v>
+      </c>
+      <c r="C292" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D292" t="n">
+        <v>5.369359970092773</v>
+      </c>
+      <c r="E292" t="n">
+        <v>154853.8601589499</v>
+      </c>
+      <c r="F292" t="n">
+        <v>3</v>
+      </c>
+      <c r="G292" t="n">
+        <v>3</v>
+      </c>
+      <c r="H292" t="n">
+        <v>2</v>
+      </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>20</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D293" t="n">
+        <v>4.914268732070923</v>
+      </c>
+      <c r="E293" t="n">
+        <v>158856.0589829469</v>
+      </c>
+      <c r="F293" t="n">
+        <v>3</v>
+      </c>
+      <c r="G293" t="n">
+        <v>4</v>
+      </c>
+      <c r="H293" t="n">
+        <v>2</v>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>20</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D294" t="n">
+        <v>7.638164281845093</v>
+      </c>
+      <c r="E294" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F294" t="n">
+        <v>3</v>
+      </c>
+      <c r="G294" t="n">
+        <v>3</v>
+      </c>
+      <c r="H294" t="n">
+        <v>2</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>20</v>
+      </c>
+      <c r="C295" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D295" t="n">
+        <v>5.732264041900635</v>
+      </c>
+      <c r="E295" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F295" t="n">
+        <v>3</v>
+      </c>
+      <c r="G295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" t="n">
+        <v>2</v>
+      </c>
+      <c r="I295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>20</v>
+      </c>
+      <c r="C296" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>8.568252801895142</v>
+      </c>
+      <c r="E296" t="n">
+        <v>163556.1244363221</v>
+      </c>
+      <c r="F296" t="n">
+        <v>3</v>
+      </c>
+      <c r="G296" t="n">
+        <v>5</v>
+      </c>
+      <c r="H296" t="n">
+        <v>2</v>
+      </c>
+      <c r="I296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>20</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D297" t="n">
+        <v>7.742295742034912</v>
+      </c>
+      <c r="E297" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F297" t="n">
+        <v>3</v>
+      </c>
+      <c r="G297" t="n">
+        <v>3</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>20</v>
+      </c>
+      <c r="C298" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D298" t="n">
+        <v>7.619564771652222</v>
+      </c>
+      <c r="E298" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F298" t="n">
+        <v>3</v>
+      </c>
+      <c r="G298" t="n">
+        <v>5</v>
+      </c>
+      <c r="H298" t="n">
+        <v>2</v>
+      </c>
+      <c r="I298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>20</v>
+      </c>
+      <c r="C299" t="n">
+        <v>4</v>
+      </c>
+      <c r="D299" t="n">
+        <v>5.75236177444458</v>
+      </c>
+      <c r="E299" t="n">
+        <v>159038.7198662622</v>
+      </c>
+      <c r="F299" t="n">
+        <v>3</v>
+      </c>
+      <c r="G299" t="n">
+        <v>3</v>
+      </c>
+      <c r="H299" t="n">
+        <v>2</v>
+      </c>
+      <c r="I299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>20</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D300" t="n">
+        <v>9.036612749099731</v>
+      </c>
+      <c r="E300" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F300" t="n">
+        <v>3</v>
+      </c>
+      <c r="G300" t="n">
+        <v>5</v>
+      </c>
+      <c r="H300" t="n">
+        <v>2</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>13/04/2026 17:54:34</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>20</v>
+      </c>
+      <c r="C301" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D301" t="n">
+        <v>8.722434997558594</v>
+      </c>
+      <c r="E301" t="n">
+        <v>163556.1251849869</v>
+      </c>
+      <c r="F301" t="n">
+        <v>3</v>
+      </c>
+      <c r="G301" t="n">
+        <v>5</v>
+      </c>
+      <c r="H301" t="n">
+        <v>2</v>
+      </c>
+      <c r="I301" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
